--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>96333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R3" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +895,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R4" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +960,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1142,12 +1112,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R6" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1212,19 +1177,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1213,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R7" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1328,19 +1278,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>96353</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R2" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -996,12 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352880.805359847</v>
+        <v>352881</v>
       </c>
       <c r="R5" t="n">
-        <v>6357610.833357252</v>
+        <v>6357611</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1066,19 +1046,9 @@
           <t>1987-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1987-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109398</v>
+        <v>109413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109413</v>
+        <v>109422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98640</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97493</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106244</v>
+        <v>106257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4289540</v>
       </c>
       <c r="B2" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3558049</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4235095</v>
       </c>
       <c r="B4" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>3240267</v>
       </c>
       <c r="B5" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>4191006</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>2773322</v>
       </c>
       <c r="B7" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54503-2024 artfynd.xlsx
+++ b/artfynd/A 54503-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4289540</v>
+        <v>2773322</v>
       </c>
       <c r="B2" t="n">
-        <v>98667</v>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3558049</v>
+        <v>3240267</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4235095</v>
+        <v>3558049</v>
       </c>
       <c r="B4" t="n">
-        <v>97520</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,27 +978,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3240267</v>
+        <v>4191006</v>
       </c>
       <c r="B5" t="n">
-        <v>106271</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4191006</v>
+        <v>4235095</v>
       </c>
       <c r="B6" t="n">
-        <v>97517</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2773322</v>
+        <v>4289540</v>
       </c>
       <c r="B7" t="n">
-        <v>109505</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
